--- a/sources/anna_step6b.xlsx
+++ b/sources/anna_step6b.xlsx
@@ -423,7 +423,7 @@
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -2579,12 +2579,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>– 1,4,2 [~U_~D]</t>
+          <t>– 1,4,2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>– Snake</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4912,12 +4917,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>– 4&lt;2 [~U_~D]</t>
+          <t>– 4&lt;2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>– Snake</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5192,12 +5202,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS]</t>
+          <t>Creeping Snake</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5571,12 +5586,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>–– 4&lt;2 [~U_~D]</t>
+          <t>–– 4&lt;2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>–– Snake [SS]</t>
+          <t>–– Snake</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5895,12 +5915,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>uf+4,3,4 [~U_~D]</t>
+          <t>uf+4,3,4</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Can Opener [SS]</t>
+          <t>Can Opener</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5957,12 +5982,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>d+4&lt;1 [~U_~D]</t>
+          <t>d+4&lt;1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6019,12 +6049,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">

--- a/sources/anna_step6b.xlsx
+++ b/sources/anna_step6b.xlsx
@@ -837,6 +837,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
@@ -884,6 +889,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
@@ -929,6 +939,11 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>31ad5619-ed1a-41f7-95e0-e44eadc9aed1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -6976,6 +6991,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
+        </is>
+      </c>
       <c r="R122" t="inlineStr">
         <is>
           <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
@@ -7013,6 +7033,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
+        </is>
+      </c>
       <c r="R123" t="inlineStr">
         <is>
           <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
@@ -7055,6 +7080,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
+        </is>
+      </c>
       <c r="R124" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
@@ -7097,6 +7127,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
+        </is>
+      </c>
       <c r="R125" t="inlineStr">
         <is>
           <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
@@ -7139,6 +7174,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
+        </is>
+      </c>
       <c r="R126" t="inlineStr">
         <is>
           <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
@@ -7181,6 +7221,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
+        </is>
+      </c>
       <c r="R127" t="inlineStr">
         <is>
           <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
@@ -7223,6 +7268,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
+        </is>
+      </c>
       <c r="R128" t="inlineStr">
         <is>
           <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
@@ -7265,6 +7315,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>93714c88-336b-411f-b863-f65c2a39733a</t>
+        </is>
+      </c>
       <c r="R129" t="inlineStr">
         <is>
           <t>93714c88-336b-411f-b863-f65c2a39733a</t>
@@ -7305,6 +7360,11 @@
       <c r="M130" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>0e938de5-6095-4002-9ade-581f69b50247</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -7452,6 +7512,11 @@
       <c r="K134" t="inlineStr">
         <is>
           <t>hhhhhlhhhh</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>d61c2d77-39a1-494e-8996-5a62586356a9</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">

--- a/sources/anna_step6b.xlsx
+++ b/sources/anna_step6b.xlsx
@@ -2830,6 +2830,11 @@
           <t>– 1,b+4</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1,db+4; 1,d+4</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>– Jab Rush - Low Kick</t>
